--- a/04_GD32F407_FreeRTOS_BinarySemaphore2/Project/GD32F407_analysis.xlsx
+++ b/04_GD32F407_FreeRTOS_BinarySemaphore2/Project/GD32F407_analysis.xlsx
@@ -401,10 +401,10 @@
                   <c:v>timers.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>gd32f4xx_usart.o</c:v>
@@ -494,100 +494,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>25.07060813903809</c:v>
+                  <c:v>24.96566200256348</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.97536945343018</c:v>
+                  <c:v>14.91268253326416</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.784893035888672</c:v>
+                  <c:v>6.756491661071777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.292282581329346</c:v>
+                  <c:v>6.265943050384522</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.167487621307373</c:v>
+                  <c:v>6.14167070388794</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.361248016357422</c:v>
+                  <c:v>4.473804473876953</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.072249412536621</c:v>
+                  <c:v>4.342991828918457</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.888341426849365</c:v>
+                  <c:v>3.872064828872681</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.862068891525269</c:v>
+                  <c:v>3.84590220451355</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.704433441162109</c:v>
+                  <c:v>3.688926696777344</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.507389068603516</c:v>
+                  <c:v>3.492707252502441</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.087028026580811</c:v>
+                  <c:v>3.074105501174927</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.850574731826782</c:v>
+                  <c:v>2.838642120361328</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.811165809631348</c:v>
+                  <c:v>2.799398183822632</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.891625642776489</c:v>
+                  <c:v>1.883707284927368</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.799671649932861</c:v>
+                  <c:v>1.79213809967041</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.182265996932983</c:v>
+                  <c:v>1.177317023277283</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.9852216839790344</c:v>
+                  <c:v>0.9810975193977356</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.6436781883239746</c:v>
+                  <c:v>0.6409837007522583</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.3152709305286408</c:v>
+                  <c:v>0.3139511942863464</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2364532053470612</c:v>
+                  <c:v>0.235463410615921</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2364532053470612</c:v>
+                  <c:v>0.235463410615921</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2364532053470612</c:v>
+                  <c:v>0.235463410615921</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2101806253194809</c:v>
+                  <c:v>0.2093008011579514</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1970443278551102</c:v>
+                  <c:v>0.1962195038795471</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1970443278551102</c:v>
+                  <c:v>0.1962195038795471</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1970443278551102</c:v>
+                  <c:v>0.1962195038795471</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.07881773263216019</c:v>
+                  <c:v>0.07848779857158661</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.05254515632987022</c:v>
+                  <c:v>0.05232520028948784</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.05254515632987022</c:v>
+                  <c:v>0.05232520028948784</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02627257816493511</c:v>
+                  <c:v>0.02616260014474392</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.02627257816493511</c:v>
+                  <c:v>0.02616260014474392</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -1216,10 +1216,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="1">
-        <v>620</v>
+        <v>684</v>
       </c>
       <c r="E9" s="1">
-        <v>620</v>
+        <v>684</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>25.07060813903809</v>
+        <v>24.96566200256348</v>
       </c>
       <c r="C3" s="1">
         <v>3817</v>
@@ -1447,7 +1447,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>14.97536945343018</v>
+        <v>14.91268253326416</v>
       </c>
       <c r="C4" s="1">
         <v>2280</v>
@@ -1473,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>6.784893035888672</v>
+        <v>6.756491661071777</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -1499,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>6.292282581329346</v>
+        <v>6.265943050384522</v>
       </c>
       <c r="C6" s="1">
         <v>958</v>
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>6.167487621307373</v>
+        <v>6.14167070388794</v>
       </c>
       <c r="C7" s="1">
         <v>939</v>
@@ -1548,54 +1548,54 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>4.361248016357422</v>
+        <v>4.473804473876953</v>
       </c>
       <c r="C8" s="1">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="D8" s="1">
-        <v>76828</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
-        <v>626</v>
+        <v>684</v>
       </c>
       <c r="F8" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>76828</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.072249412536621</v>
+        <v>4.342991828918457</v>
       </c>
       <c r="C9" s="1">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="D9" s="1">
-        <v>16</v>
+        <v>76828</v>
       </c>
       <c r="E9" s="1">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>16</v>
+        <v>76828</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1603,7 +1603,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>3.888341426849365</v>
+        <v>3.872064828872681</v>
       </c>
       <c r="C10" s="1">
         <v>592</v>
@@ -1629,7 +1629,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>3.862068891525269</v>
+        <v>3.84590220451355</v>
       </c>
       <c r="C11" s="1">
         <v>588</v>
@@ -1655,7 +1655,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>3.704433441162109</v>
+        <v>3.688926696777344</v>
       </c>
       <c r="C12" s="1">
         <v>564</v>
@@ -1681,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.507389068603516</v>
+        <v>3.492707252502441</v>
       </c>
       <c r="C13" s="1">
         <v>534</v>
@@ -1707,7 +1707,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>3.087028026580811</v>
+        <v>3.074105501174927</v>
       </c>
       <c r="C14" s="1">
         <v>470</v>
@@ -1733,7 +1733,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>2.850574731826782</v>
+        <v>2.838642120361328</v>
       </c>
       <c r="C15" s="1">
         <v>434</v>
@@ -1759,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>2.811165809631348</v>
+        <v>2.799398183822632</v>
       </c>
       <c r="C16" s="1">
         <v>428</v>
@@ -1785,7 +1785,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.891625642776489</v>
+        <v>1.883707284927368</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1811,7 +1811,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>1.799671649932861</v>
+        <v>1.79213809967041</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1837,7 +1837,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>1.182265996932983</v>
+        <v>1.177317023277283</v>
       </c>
       <c r="C19" s="1">
         <v>180</v>
@@ -1863,7 +1863,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>0.9852216839790344</v>
+        <v>0.9810975193977356</v>
       </c>
       <c r="C20" s="1">
         <v>150</v>
@@ -1889,7 +1889,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>0.6436781883239746</v>
+        <v>0.6409837007522583</v>
       </c>
       <c r="C21" s="1">
         <v>98</v>
@@ -1915,7 +1915,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.3152709305286408</v>
+        <v>0.3139511942863464</v>
       </c>
       <c r="C22" s="1">
         <v>48</v>
@@ -1941,7 +1941,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2364532053470612</v>
+        <v>0.235463410615921</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1967,7 +1967,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2364532053470612</v>
+        <v>0.235463410615921</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1993,7 +1993,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2364532053470612</v>
+        <v>0.235463410615921</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2019,7 +2019,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2101806253194809</v>
+        <v>0.2093008011579514</v>
       </c>
       <c r="C26" s="1">
         <v>32</v>
@@ -2045,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1970443278551102</v>
+        <v>0.1962195038795471</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -2071,7 +2071,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1970443278551102</v>
+        <v>0.1962195038795471</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2097,7 +2097,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1970443278551102</v>
+        <v>0.1962195038795471</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -2123,7 +2123,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.07881773263216019</v>
+        <v>0.07848779857158661</v>
       </c>
       <c r="C30" s="1">
         <v>12</v>
@@ -2149,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.05254515632987022</v>
+        <v>0.05232520028948784</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -2175,7 +2175,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.05254515632987022</v>
+        <v>0.05232520028948784</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
@@ -2201,7 +2201,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02627257816493511</v>
+        <v>0.02616260014474392</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
@@ -2227,7 +2227,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.02627257816493511</v>
+        <v>0.02616260014474392</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>
